--- a/zhipu/docs/reports/20261022_v0.1.1_TK同步_對照.xlsx
+++ b/zhipu/docs/reports/20261022_v0.1.1_TK同步_對照.xlsx
@@ -24990,7 +24990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -25030,1078 +25030,376 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>輸出</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>Tokenomics 提交</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>v0.1</t>
+          <t>開工時 master HEAD `1916a06`（CURRENT 為 v19.0，與工作單 `ad33e28` 為同一檔）</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>v0.1.1</t>
+          <t>`ad33e28`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>差額</t>
+          <t>無（檔案 SHA-256 相同）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>η 2025</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OpenAI 快照</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>1.126</t>
+          <t>main 上 `openai/model/CURRENT`＝v0.6.2（`--oai-ref main@f645e19`）</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>PR #62 分支</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>-0.126</t>
+          <t>僅並排數字：OpenAI 2030 覆蓋率 0.457、累計外部資金需求 $442.8B（v0.6 為 0.46、$443B），結論不變</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>η 1H26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>`IF_AllocRDGW` 使用點值或區間</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3.908</t>
+          <t>基準用點值 0.203；區間端點只並列（Checks C97–C98）</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3.137</t>
+          <t>以端點驅動</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0.771</t>
+          <t>0（該名稱不驅動任何輸出，已重算證明）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>token 換算 GW（÷η 前）</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>`RNG_*` 三名稱</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2.108</t>
+          <t>新增為 TK_Link 工程類名稱，Checks C99 驗證 `RNG_StaleFlag`＝『一致』</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1.692</t>
+          <t>不新增</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0.416</t>
+          <t>無</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>有效推論 GW（未截頂）</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>國產晶片產能</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>沿用「Hopper × 比例」暫代；Hopper 欄隨新版改變</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>重估國產欄</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>機隊 VR 等值係數 0.056 → 0.065；2030 每 VR 等值 GW 差額 +338 RMB 億（①）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>研發 GW（殘差）</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>η 2025 觸及下限</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>沿用 `MAX(INP_138＝1, 校準值)`，不改機制</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>允許 η&lt;1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2025 η 1.126 → 1.000；2025 研發占比 30% → 36.7%；2026 起無影響</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>研發占總需求比</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>容量截頂</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0.300</t>
+          <t>照既有機制；截頂係數各年 1.000，未觸發</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>無</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>機隊 VR 等值係數</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Checks 標籤更正</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>舊 C08（標籤『同 OpenAI v0.6 的 63 名』）退役，取新號 C96；退役不重用</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>沿用 C08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>無</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>供給 VR 等值 GW</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>歸因分組</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>依工作單五組；②含 `IF_CapexTotal`（對基準無影響：自建 GW 為 0）；`IF_DeprLifeIT` 值未變</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>其他分組</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>無</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>推論算力成本 RMB 億</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>敏感度與翻轉點</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17.066</t>
+          <t>以新 Excel 重算（`sensitivity_z4.py`＋`sensitivity_r2.yaml`），HTML 改引用新 JSON</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15.431</t>
+          <t>沿用舊 JSON</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1.635</t>
+          <t>翻轉點移動（第 5 節）；沿用舊值會令 HTML 與 Excel 不符</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>研發算力成本 RMB 億</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>`kw_hopper`（Inputs，引用 v5.26 DC_Cost）</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7.314</t>
+          <t>不改（Excel 擁有；v19.0 DC_Cost 同值）</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8.949</t>
+          <t>改註記</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>無</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>算力成本合計 RMB 億</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>引擎檔名規則</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>361.210</t>
+          <t>`engine/core.py` `MODEL_NAME_RE` 放寬為允許三段版號（`v0.1.1`）</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>347.034</t>
+          <t>檔名改兩段</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14.177</t>
+          <t>無（工程類）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>供應商持有成本 RMB 億</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>HTML 敘述</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>361.210</t>
+          <t>數字皆讀 Excel；「η 範圍兩項」WARN 字樣改為一項（C55）</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>347.034</t>
+          <t>不改</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-14.177</t>
+          <t>文字與 Checks 一致</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>雲端毛利 %</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>本段不改公司層級輸入與機制（規格 D1–D26）</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>照工作單</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0.031</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>雲端毛利 %</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0.043</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0.075</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0.032</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>雲端毛利 %</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>每 VR 等值 GW 差額 RMB 億（命題 1）</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-15,529.4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-13,338.5</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2,191.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>每 VR 等值 GW 差額 RMB 億（命題 1）</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-3,506.2</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-2,970.1</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>536.019</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>每 VR 等值 GW 差額 RMB 億（命題 1）</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>-2,394.0</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-1,803.6</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>590.369</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>每 VR 等值 GW 差額 $B</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>-35.519</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>-26.760</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>8.759</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>每實體 GW 差額 RMB 億</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>-134.426</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-117.911</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>16.515</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>每實體 GW 差額 $B</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>-1.994</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>-1.749</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0.245</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>營收覆蓋全成本比</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>0.708</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>0.734</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0.026</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>累計外部資金需求 RMB 億（命題 2）</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>43.555</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>7.486</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>-36.069</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>外部資金需求峰值年</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>年底現金 RMB 億</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>193.935</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>186.847</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>-7.088</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Tokenomics 提交</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>開工時 master HEAD `1916a06`（CURRENT 為 v19.0，與工作單 `ad33e28` 為同一檔）</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>`ad33e28`</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>無（檔案 SHA-256 相同）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>OpenAI 快照</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>main 上 `openai/model/CURRENT`＝v0.6.2（`--oai-ref main@f645e19`）</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>PR #62 分支</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>僅並排數字：OpenAI 2030 覆蓋率 0.457、累計外部資金需求 $442.8B（v0.6 為 0.46、$443B），結論不變</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>`IF_AllocRDGW` 使用點值或區間</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>基準用點值 0.203；區間端點只並列（Checks C97–C98）</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>以端點驅動</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>0（該名稱不驅動任何輸出，已重算證明）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>`RNG_*` 三名稱</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>新增為 TK_Link 工程類名稱，Checks C99 驗證 `RNG_StaleFlag`＝『一致』</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>不新增</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>國產晶片產能</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>沿用「Hopper × 比例」暫代；Hopper 欄隨新版改變</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>重估國產欄</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>機隊 VR 等值係數 0.056 → 0.065；2030 每 VR 等值 GW 差額 +338 RMB 億（①）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>η 2025 觸及下限</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>沿用 `MAX(INP_138＝1, 校準值)`，不改機制</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>允許 η&lt;1</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>2025 η 1.126 → 1.000；2025 研發占比 30% → 36.7%；2026 起無影響</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>容量截頂</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>照既有機制；截頂係數各年 1.000，未觸發</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Checks 標籤更正</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>舊 C08（標籤『同 OpenAI v0.6 的 63 名』）退役，取新號 C96；退役不重用</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>沿用 C08</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>歸因分組</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>依工作單五組；②含 `IF_CapexTotal`（對基準無影響：自建 GW 為 0）；`IF_DeprLifeIT` 值未變</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>其他分組</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>敏感度與翻轉點</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>以新 Excel 重算（`sensitivity_z4.py`＋`sensitivity_r2.yaml`），HTML 改引用新 JSON</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>沿用舊 JSON</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>翻轉點移動（第 5 節）；沿用舊值會令 HTML 與 Excel 不符</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>`kw_hopper`（Inputs，引用 v5.26 DC_Cost）</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>不改（Excel 擁有；v19.0 DC_Cost 同值）</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>改註記</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>引擎檔名規則</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>`engine/core.py` `MODEL_NAME_RE` 放寬為允許三段版號（`v0.1.1`）</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>檔名改兩段</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>無（工程類）</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>HTML 敘述</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>數字皆讀 Excel；「η 範圍兩項」WARN 字樣改為一項（C55）</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>不改</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>文字與 Checks 一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>本段不改公司層級輸入與機制（規格 D1–D26）</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>照工作單</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
